--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104747_W33.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104747_W33.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7521</v>
+        <v>6.0971</v>
       </c>
       <c r="E2" t="n">
-        <v>6.348</v>
+        <v>5.7557</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4041</v>
+        <v>0.3414</v>
       </c>
       <c r="G2" t="n">
         <v>1.3411</v>
@@ -610,13 +610,13 @@
         <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>3.0938</v>
+        <v>2.4389</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4942</v>
+        <v>1.902</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5996</v>
+        <v>0.5369</v>
       </c>
       <c r="V2" t="n">
         <v>1.6342</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.3245</v>
+        <v>5.8924</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4538</v>
+        <v>5.9276</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1293</v>
+        <v>-0.0352</v>
       </c>
       <c r="G3" t="n">
         <v>3.0145</v>
@@ -688,13 +688,13 @@
         <v>1.8211</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9733000000000001</v>
+        <v>1.5411</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6176</v>
+        <v>1.0914</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3557</v>
+        <v>0.4498</v>
       </c>
       <c r="V3" t="n">
         <v>1.792</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.006</v>
+        <v>3.2115</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0266</v>
+        <v>2.2635</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9792999999999999</v>
+        <v>0.948</v>
       </c>
       <c r="G4" t="n">
         <v>-0.1457</v>
@@ -766,13 +766,13 @@
         <v>2.0487</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0802</v>
+        <v>1.2857</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7058</v>
+        <v>0.9427</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3744</v>
+        <v>0.343</v>
       </c>
       <c r="V4" t="n">
         <v>1.1609</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. KRAVISH</t>
+          <t>O. BALCEROWSKI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6048</v>
+        <v>2.7002</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6191</v>
+        <v>3.8657</v>
       </c>
       <c r="F5" t="n">
-        <v>3.2239</v>
+        <v>-1.1655</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8259</v>
+        <v>3.2565</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8788</v>
+        <v>4.2543</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0529</v>
+        <v>-0.9977</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5621</v>
+        <v>5.2179</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1454</v>
+        <v>4.3987</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7075</v>
+        <v>0.8192</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2638</v>
+        <v>-1.9613</v>
       </c>
       <c r="N5" t="n">
-        <v>2.0242</v>
+        <v>-0.1444</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.7604</v>
+        <v>-1.8169</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.8211</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.4145</v>
+        <v>-2.2763</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5934</v>
+        <v>1.1382</v>
       </c>
       <c r="S5" t="n">
-        <v>2.1236</v>
+        <v>1.6713</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5991</v>
+        <v>0.9242</v>
       </c>
       <c r="U5" t="n">
-        <v>1.5245</v>
+        <v>0.7471</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4764</v>
+        <v>-1.0895</v>
       </c>
       <c r="W5" t="n">
-        <v>1.6342</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1578</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. BALCEROWSKI</t>
+          <t>D. KRAVISH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4947</v>
+        <v>1.9078</v>
       </c>
       <c r="E6" t="n">
-        <v>3.6288</v>
+        <v>-0.5006</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1342</v>
+        <v>2.4084</v>
       </c>
       <c r="G6" t="n">
-        <v>3.2565</v>
+        <v>0.8259</v>
       </c>
       <c r="H6" t="n">
-        <v>4.2543</v>
+        <v>1.8788</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9977</v>
+        <v>-1.0529</v>
       </c>
       <c r="J6" t="n">
-        <v>5.2179</v>
+        <v>0.5621</v>
       </c>
       <c r="K6" t="n">
-        <v>4.3987</v>
+        <v>-0.1454</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8192</v>
+        <v>0.7075</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.9613</v>
+        <v>0.2638</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1444</v>
+        <v>2.0242</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.8169</v>
+        <v>-1.7604</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.1382</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2763</v>
+        <v>-3.4145</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1382</v>
+        <v>1.5934</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4658</v>
+        <v>1.4265</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6873</v>
+        <v>0.7175</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7785</v>
+        <v>0.709</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0895</v>
+        <v>1.4764</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.6342</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0895</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="7">
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.937</v>
+        <v>1.4633</v>
       </c>
       <c r="E7" t="n">
-        <v>2.9753</v>
+        <v>2.5015</v>
       </c>
       <c r="F7" t="n">
         <v>-1.0383</v>
@@ -1000,10 +1000,10 @@
         <v>0.2276</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9617</v>
+        <v>0.4879</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6688</v>
+        <v>0.195</v>
       </c>
       <c r="U7" t="n">
         <v>0.2929</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6345</v>
+        <v>0.781</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5323</v>
+        <v>-1.4798</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1667</v>
+        <v>2.2608</v>
       </c>
       <c r="G8" t="n">
         <v>-0.9878</v>
@@ -1078,13 +1078,13 @@
         <v>2.5039</v>
       </c>
       <c r="S8" t="n">
-        <v>3.5328</v>
+        <v>2.6793</v>
       </c>
       <c r="T8" t="n">
-        <v>3.1444</v>
+        <v>2.1969</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3883</v>
+        <v>0.4824</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. TILLIE</t>
+          <t>N. DJEDOVIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5696</v>
+        <v>-0.5253</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1752</v>
+        <v>0.2951</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7447</v>
+        <v>-0.8204</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5696</v>
+        <v>0.9716</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0172</v>
+        <v>1.7805</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5868</v>
+        <v>-0.8089</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0172</v>
+        <v>1.2265</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0172</v>
+        <v>0.8618</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.3647</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5868</v>
+        <v>-0.2549</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>0.9187</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5868</v>
+        <v>-1.1736</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.186</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1579</v>
+        <v>0.2067</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1579</v>
+        <v>-0.0207</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. DJEDOVIC</t>
+          <t>K. TILLIE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7065</v>
+        <v>-0.5696</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1766</v>
+        <v>0.1752</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8831</v>
+        <v>-0.7447</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9716</v>
+        <v>-0.5696</v>
       </c>
       <c r="H10" t="n">
-        <v>1.7805</v>
+        <v>0.0172</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8089</v>
+        <v>-0.5868</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2265</v>
+        <v>0.0172</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8618</v>
+        <v>0.0172</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3647</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2549</v>
+        <v>-0.5868</v>
       </c>
       <c r="N10" t="n">
-        <v>0.9187</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1736</v>
+        <v>-0.5868</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.1382</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1382</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0048</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0882</v>
+        <v>0.1579</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0834</v>
+        <v>-0.1579</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5447</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5447</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3233</v>
+        <v>-2.1107</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4636</v>
+        <v>-1.3452</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8596</v>
+        <v>-0.7655</v>
       </c>
       <c r="G11" t="n">
         <v>-0.1028</v>
@@ -1312,13 +1312,13 @@
         <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1453</v>
+        <v>1.3579</v>
       </c>
       <c r="T11" t="n">
-        <v>0.757</v>
+        <v>0.8754</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3883</v>
+        <v>0.4824</v>
       </c>
       <c r="V11" t="n">
         <v>-1.0895</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.0011</v>
+        <v>-2.6945</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3122</v>
+        <v>-1.6015</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.689</v>
+        <v>-1.093</v>
       </c>
       <c r="G12" t="n">
         <v>-0.259</v>
@@ -1390,13 +1390,13 @@
         <v>1.3658</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6526</v>
+        <v>0.654</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.33</v>
+        <v>0.3807</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3226</v>
+        <v>0.2733</v>
       </c>
       <c r="V12" t="n">
         <v>-2.1789</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1531</v>
+        <v>16.15319999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>15.8571</v>
+        <v>15.8572</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2957999999999994</v>
+        <v>0.2960000000000003</v>
       </c>
       <c r="G13" t="n">
         <v>7.776899999999999</v>
@@ -1447,13 +1447,13 @@
         <v>11.3528</v>
       </c>
       <c r="L13" t="n">
-        <v>7.846000000000001</v>
+        <v>7.845999999999999</v>
       </c>
       <c r="M13" t="n">
         <v>-11.4218</v>
       </c>
       <c r="N13" t="n">
-        <v>9.399000000000001</v>
+        <v>9.398999999999999</v>
       </c>
       <c r="O13" t="n">
         <v>-20.8206</v>
@@ -1468,16 +1468,16 @@
         <v>13.658</v>
       </c>
       <c r="S13" t="n">
-        <v>13.7287</v>
+        <v>13.7286</v>
       </c>
       <c r="T13" t="n">
-        <v>9.590300000000001</v>
+        <v>9.590399999999997</v>
       </c>
       <c r="U13" t="n">
-        <v>4.138299999999999</v>
+        <v>4.1382</v>
       </c>
       <c r="V13" t="n">
-        <v>1.476399999999999</v>
+        <v>1.4764</v>
       </c>
       <c r="W13" t="n">
         <v>7.5548</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4764</v>
+        <v>1.7538</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8844</v>
+        <v>2.0029</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4081</v>
+        <v>-0.2491</v>
       </c>
       <c r="G14" t="n">
         <v>0.1936</v>
@@ -1546,13 +1546,13 @@
         <v>2.0487</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3124</v>
+        <v>-1.0349</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3256</v>
+        <v>-0.2072</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9868</v>
+        <v>-0.8278</v>
       </c>
       <c r="V14" t="n">
         <v>1.9122</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0784</v>
+        <v>1.133</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7467</v>
+        <v>2.3914</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6683</v>
+        <v>-1.2584</v>
       </c>
       <c r="G15" t="n">
         <v>2.1744</v>
@@ -1624,13 +1624,13 @@
         <v>0.2276</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8293</v>
+        <v>-0.7747000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3714</v>
+        <v>0.0161</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.2007</v>
+        <v>-0.7907</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2667</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. ARANITOVIC</t>
+          <t>I. CRUZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.178</v>
+        <v>0.4091</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1962</v>
+        <v>0.7884</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0182</v>
+        <v>-0.3793</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.7488</v>
+        <v>0.6435999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.3186</v>
+        <v>-0.6867</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4302</v>
+        <v>1.3302</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5322</v>
+        <v>1.2461</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6516999999999999</v>
+        <v>0.0172</v>
       </c>
       <c r="L16" t="n">
-        <v>1.1839</v>
+        <v>1.2288</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.2809</v>
+        <v>-0.6025</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.6668</v>
+        <v>-0.7039</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.6141</v>
+        <v>0.1014</v>
       </c>
       <c r="P16" t="n">
-        <v>2.0487</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1382</v>
+        <v>-0.2276</v>
       </c>
       <c r="R16" t="n">
-        <v>3.1868</v>
+        <v>0.2276</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.3009</v>
+        <v>-0.1255</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3768</v>
+        <v>-0.2301</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9241</v>
+        <v>0.1046</v>
       </c>
       <c r="V16" t="n">
-        <v>2.1789</v>
+        <v>-0.1089</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1789</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. CRUZ</t>
+          <t>A. ARANITOVIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1942</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6699000000000001</v>
+        <v>0.9593</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5999</v>
+        <v>-0.7651</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6435999999999999</v>
+        <v>-2.7488</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6867</v>
+        <v>-2.3186</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3302</v>
+        <v>-0.4302</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2461</v>
+        <v>0.5322</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0172</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2288</v>
+        <v>1.1839</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6025</v>
+        <v>-3.2809</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7039</v>
+        <v>-1.6668</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1014</v>
+        <v>-1.6141</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.0487</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2276</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2276</v>
+        <v>3.1868</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4646</v>
+        <v>-1.2846</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3485</v>
+        <v>-0.6137</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1161</v>
+        <v>-0.671</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1089</v>
+        <v>2.1789</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1089</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5501</v>
+        <v>-0.3526</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7175</v>
+        <v>-0.8359</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1674</v>
+        <v>0.4833</v>
       </c>
       <c r="G18" t="n">
         <v>-0.6176</v>
@@ -1858,13 +1858,13 @@
         <v>1.8211</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.417</v>
+        <v>-1.2196</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1862</v>
+        <v>-0.3046</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.2308</v>
+        <v>-0.9149</v>
       </c>
       <c r="V18" t="n">
         <v>-0.1089</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5798</v>
+        <v>-0.9676</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7796999999999999</v>
+        <v>-1.6088</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1999</v>
+        <v>0.6412</v>
       </c>
       <c r="G19" t="n">
         <v>-1.5087</v>
@@ -1936,13 +1936,13 @@
         <v>1.5934</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4736</v>
+        <v>0.0858</v>
       </c>
       <c r="T19" t="n">
-        <v>1.1796</v>
+        <v>0.3505</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.706</v>
+        <v>-0.2647</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0539</v>
+        <v>-1.5093</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8064</v>
+        <v>-1.4511</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2475</v>
+        <v>-0.0582</v>
       </c>
       <c r="G20" t="n">
         <v>0.2527</v>
@@ -2014,13 +2014,13 @@
         <v>1.8211</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7131999999999999</v>
+        <v>-0.1685</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6088</v>
+        <v>-0.2535</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1044</v>
+        <v>0.0849</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1142</v>
+        <v>-1.522</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8817</v>
+        <v>-0.7632</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2326</v>
+        <v>-0.7588</v>
       </c>
       <c r="G21" t="n">
         <v>-3.466</v>
@@ -2092,13 +2092,13 @@
         <v>2.9592</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.5181</v>
+        <v>-1.9259</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8135</v>
+        <v>-0.6951000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.7046</v>
+        <v>-1.2308</v>
       </c>
       <c r="V21" t="n">
         <v>1.1383</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. ANDRIC</t>
+          <t>D. BRANKOVIC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,40 +2125,40 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.8697</v>
+        <v>-3.2915</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9166</v>
+        <v>1.0045</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.9531</v>
+        <v>-4.296</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.189</v>
+        <v>1.0386</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.2299</v>
+        <v>-1.2033</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9592000000000001</v>
+        <v>2.2419</v>
       </c>
       <c r="J22" t="n">
-        <v>1.1789</v>
+        <v>2.9723</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8963</v>
+        <v>-0.7141999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2826</v>
+        <v>3.6864</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.3679</v>
+        <v>-1.9337</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.1262</v>
+        <v>-0.4891</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.2417</v>
+        <v>-1.4446</v>
       </c>
       <c r="P22" t="n">
         <v>1.1382</v>
@@ -2170,28 +2170,28 @@
         <v>2.2763</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1846</v>
+        <v>-2.1998</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9573</v>
+        <v>-0.8296</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2272</v>
+        <v>-1.3702</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.6342</v>
+        <v>-3.2684</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.6342</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. BRANKOVIC</t>
+          <t>M. ANDRIC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,40 +2203,40 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9302</v>
+        <v>-3.4494</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6492</v>
+        <v>-0.5613</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.5794</v>
+        <v>-2.8881</v>
       </c>
       <c r="G23" t="n">
-        <v>1.0386</v>
+        <v>-2.189</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.2033</v>
+        <v>-1.2299</v>
       </c>
       <c r="I23" t="n">
-        <v>2.2419</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>2.9723</v>
+        <v>1.1789</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.7141999999999999</v>
+        <v>0.8963</v>
       </c>
       <c r="L23" t="n">
-        <v>3.6864</v>
+        <v>0.2826</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.9337</v>
+        <v>-3.3679</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4891</v>
+        <v>-2.1262</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.4446</v>
+        <v>-1.2417</v>
       </c>
       <c r="P23" t="n">
         <v>1.1382</v>
@@ -2248,22 +2248,22 @@
         <v>2.2763</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.8385</v>
+        <v>-0.7643</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.185</v>
+        <v>-0.602</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.6536</v>
+        <v>-0.1623</v>
       </c>
       <c r="V23" t="n">
-        <v>-3.2684</v>
+        <v>-1.6342</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-3.2684</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.8579</v>
+        <v>-5.3922</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.1144</v>
+        <v>-2.9959</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.7435</v>
+        <v>-2.3963</v>
       </c>
       <c r="G24" t="n">
         <v>-1.5497</v>
@@ -2326,13 +2326,13 @@
         <v>2.0487</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.6237</v>
+        <v>-1.158</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8875999999999999</v>
+        <v>-0.7692</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7361</v>
+        <v>-0.3888</v>
       </c>
       <c r="V24" t="n">
         <v>-1.3187</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-16.153</v>
+        <v>-12.9945</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.0699</v>
+        <v>-1.069700000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-15.0833</v>
+        <v>-11.9248</v>
       </c>
       <c r="G25" t="n">
         <v>-7.776900000000001</v>
@@ -2404,13 +2404,13 @@
         <v>20.4868</v>
       </c>
       <c r="S25" t="n">
-        <v>-13.7287</v>
+        <v>-10.57</v>
       </c>
       <c r="T25" t="n">
-        <v>-4.1383</v>
+        <v>-4.1384</v>
       </c>
       <c r="U25" t="n">
-        <v>-9.590399999999999</v>
+        <v>-6.431699999999999</v>
       </c>
       <c r="V25" t="n">
         <v>-1.4764</v>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104747_W33.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104747_W33.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104747_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104747_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104747_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104747_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104747_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104747_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104747_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104747_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104747_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104747_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104747_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-6.0784</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.4245</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104747_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.2667</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104747_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104747_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104747_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104747_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104747_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104747_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.6536999999999999</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104747_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104747_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104747_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104747_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-6.7809</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
